--- a/filer/89563518_carletti.xlsx
+++ b/filer/89563518_carletti.xlsx
@@ -7666,7 +7666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7742,25 +7742,21 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndAmortisationOfIntangibleAssets</t>
+          <t>fsa:CashFlowsStatement</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndAmortisationOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>22390</v>
-      </c>
+          <t>fsa:CashFlowsStatement</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n">
-        <v>35132</v>
-      </c>
-      <c r="G3" s="35" t="n"/>
-      <c r="H3" s="35" t="n">
-        <v>41716</v>
-      </c>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7775,27 +7771,21 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
+          <t>fsa:Dividend</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
+          <t>fsa:Dividend</t>
         </is>
       </c>
       <c r="D4" s="38" t="n">
-        <v>297160</v>
+        <v>10000</v>
       </c>
       <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n">
-        <v>409952</v>
-      </c>
-      <c r="G4" s="38" t="n">
-        <v>413572</v>
-      </c>
-      <c r="H4" s="38" t="n">
-        <v>413572</v>
-      </c>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
+      <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7810,24 +7800,26 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssets</t>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n">
-        <v>969</v>
-      </c>
-      <c r="G5" s="35" t="n"/>
       <c r="H5" s="35" t="n">
-        <v>1855</v>
+        <v>20</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7843,701 +7835,28 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipment</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>29214</v>
-      </c>
-      <c r="E6" s="38" t="n"/>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n">
+        <v>-674</v>
+      </c>
       <c r="F6" s="38" t="n">
-        <v>21384</v>
+        <v>-2248</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>54334</v>
+        <v>2091</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>56649</v>
+        <v>2761</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>fsa:CashFlowsStatement</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="inlineStr">
-        <is>
-          <t>fsa:CashFlowsStatement</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n">
-        <v>23768</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>31259</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>3884</v>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:Dividend</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:Dividend</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
-        <v>46</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>22</v>
-      </c>
-      <c r="G11" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="38" t="n"/>
-      <c r="I12" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ImpairmentLossesOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n">
-        <v>786</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndAmortisationOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndAmortisationOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n">
-        <v>32</v>
-      </c>
-      <c r="I14" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndDepreciationOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndDepreciationOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n">
-        <v>-1891</v>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>6113</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>1286</v>
-      </c>
-      <c r="I15" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="38" t="n"/>
-      <c r="F16" s="38" t="n">
-        <v>-14</v>
-      </c>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n">
-        <v>58</v>
-      </c>
-      <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughTransfers</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughTransfers</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n">
-        <v>2461</v>
-      </c>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>3264</v>
-      </c>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n">
-        <v>-1574</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>-4339</v>
-      </c>
-      <c r="H18" s="38" t="n">
-        <v>-670</v>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n">
-        <v>-4162</v>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>15204</v>
-      </c>
-      <c r="H19" s="35" t="n">
-        <v>3775</v>
-      </c>
-      <c r="I19" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughTransfers</t>
-        </is>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughTransfers</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="38" t="n">
-        <v>-2461</v>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IntangibleAssetsGross</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IntangibleAssetsGross</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>44502</v>
-      </c>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n">
-        <v>73177</v>
-      </c>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n">
-        <v>74610</v>
-      </c>
-      <c r="I21" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ProfitLossAfterAttributableToMinorityInterest</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ProfitLossAfterAttributableToMinorityInterest</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="38" t="n"/>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n">
-        <v>31958</v>
-      </c>
-      <c r="H22" s="38" t="n"/>
-      <c r="I22" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>fsa:PropertyPlantAndEquipmentGross</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>fsa:PropertyPlantAndEquipmentGross</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>449812</v>
-      </c>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n">
-        <v>693635</v>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>731914</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>731914</v>
-      </c>
-      <c r="I23" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
-        </is>
-      </c>
-      <c r="C24" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
-        </is>
-      </c>
-      <c r="D24" s="38" t="n"/>
-      <c r="E24" s="38" t="n">
-        <v>-674</v>
-      </c>
-      <c r="F24" s="38" t="n">
-        <v>-2248</v>
-      </c>
-      <c r="G24" s="38" t="n">
-        <v>2091</v>
-      </c>
-      <c r="H24" s="38" t="n">
-        <v>2761</v>
-      </c>
-      <c r="I24" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C26" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D26" s="38" t="n">
-        <v>329</v>
-      </c>
-      <c r="E26" s="38" t="n"/>
-      <c r="F26" s="38" t="n">
-        <v>23028</v>
-      </c>
-      <c r="G26" s="38" t="n">
-        <v>31096</v>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>3730</v>
-      </c>
-      <c r="I26" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>274</v>
-      </c>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/89563518_carletti.xlsx
+++ b/filer/89563518_carletti.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/89563518_carletti.xlsx
+++ b/filer/89563518_carletti.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_89563518" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_89563518" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_89563518" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_89563518" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -202,11 +203,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -648,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-mellem · Den uafhængige revisors erklær</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2043,49 +2044,49 @@
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
         <f>'balance_raw_89563518'!$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="11">
         <f>'balance_raw_89563518'!$C$12</f>
         <v/>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="11">
         <f>'balance_raw_89563518'!$D$12</f>
         <v/>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="11">
         <f>'balance_raw_89563518'!$E$12</f>
         <v/>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="11">
         <f>'balance_raw_89563518'!$F$12</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="9">
+      <c r="H33" s="12">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="12">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="12">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="12">
         <f>IFERROR(E33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="12">
         <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
@@ -2093,7 +2094,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Deposita</t>
+          <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
       <c r="B34" s="5">
@@ -2139,145 +2140,145 @@
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B35" s="11">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B35" s="8">
         <f>'balance_raw_89563518'!$B$14</f>
         <v/>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="8">
         <f>'balance_raw_89563518'!$C$14</f>
         <v/>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="8">
         <f>'balance_raw_89563518'!$D$14</f>
         <v/>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="8">
         <f>'balance_raw_89563518'!$E$14</f>
         <v/>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="8">
         <f>'balance_raw_89563518'!$F$14</f>
         <v/>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="12">
+      <c r="H35" s="9">
         <f>IFERROR(B35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="9">
         <f>IFERROR(C35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="9">
         <f>IFERROR(D35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="9">
         <f>IFERROR(E35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="L35" s="12">
+      <c r="L35" s="9">
         <f>IFERROR(F35/$B$35*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B36" s="11">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B36" s="5">
         <f>'balance_raw_89563518'!$B$15</f>
         <v/>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="5">
         <f>'balance_raw_89563518'!$C$15</f>
         <v/>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="5">
         <f>'balance_raw_89563518'!$D$15</f>
         <v/>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="5">
         <f>'balance_raw_89563518'!$E$15</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="5">
         <f>'balance_raw_89563518'!$F$15</f>
         <v/>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" s="12">
+      <c r="H36" s="6">
         <f>IFERROR(B36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="6">
         <f>IFERROR(C36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="6">
         <f>IFERROR(D36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="K36" s="12">
+      <c r="K36" s="6">
         <f>IFERROR(E36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="L36" s="12">
+      <c r="L36" s="6">
         <f>IFERROR(F36/$B$36*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Råvarer og hjælpematerialer</t>
-        </is>
-      </c>
-      <c r="B37" s="8">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B37" s="11">
         <f>'balance_raw_89563518'!$B$16</f>
         <v/>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="11">
         <f>'balance_raw_89563518'!$C$16</f>
         <v/>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="11">
         <f>'balance_raw_89563518'!$D$16</f>
         <v/>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="11">
         <f>'balance_raw_89563518'!$E$16</f>
         <v/>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="11">
         <f>'balance_raw_89563518'!$F$16</f>
         <v/>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" s="9">
+      <c r="H37" s="12">
         <f>IFERROR(B37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="12">
         <f>IFERROR(C37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="12">
         <f>IFERROR(D37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="12">
         <f>IFERROR(E37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="12">
         <f>IFERROR(F37/$B$37*100,"")</f>
         <v/>
       </c>
@@ -2285,7 +2286,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Varer under fremstilling</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B38" s="5">
@@ -2333,7 +2334,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Færdigvarer og handelsvarer</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -2379,49 +2380,49 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B40" s="11">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B40" s="5">
         <f>'balance_raw_89563518'!$B$19</f>
         <v/>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="5">
         <f>'balance_raw_89563518'!$C$19</f>
         <v/>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="5">
         <f>'balance_raw_89563518'!$D$19</f>
         <v/>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="5">
         <f>'balance_raw_89563518'!$E$19</f>
         <v/>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="5">
         <f>'balance_raw_89563518'!$F$19</f>
         <v/>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="12">
+      <c r="H40" s="6">
         <f>IFERROR(B40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="6">
         <f>IFERROR(C40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="6">
         <f>IFERROR(D40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="6">
         <f>IFERROR(E40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="L40" s="12">
+      <c r="L40" s="6">
         <f>IFERROR(F40/$B$40*100,"")</f>
         <v/>
       </c>
@@ -2429,7 +2430,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -2477,7 +2478,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B42" s="5">
@@ -2525,7 +2526,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Andre tilgodehavender</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -2573,7 +2574,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B44" s="5">
@@ -2619,49 +2620,49 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B45" s="11">
         <f>'balance_raw_89563518'!$B$24</f>
         <v/>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="11">
         <f>'balance_raw_89563518'!$C$24</f>
         <v/>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="11">
         <f>'balance_raw_89563518'!$D$24</f>
         <v/>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="11">
         <f>'balance_raw_89563518'!$E$24</f>
         <v/>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="11">
         <f>'balance_raw_89563518'!$F$24</f>
         <v/>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="9">
+      <c r="H45" s="12">
         <f>IFERROR(B45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="12">
         <f>IFERROR(C45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="12">
         <f>IFERROR(D45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="12">
         <f>IFERROR(E45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="12">
         <f>IFERROR(F45/$B$45*100,"")</f>
         <v/>
       </c>
@@ -2669,7 +2670,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Værdipapirer</t>
         </is>
       </c>
       <c r="B46" s="5">
@@ -2717,7 +2718,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
+          <t>Likvide beholdninger</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -2765,7 +2766,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Tilgodehavender</t>
+          <t>Omsætningsaktiver</t>
         </is>
       </c>
       <c r="B48" s="11">
@@ -2811,239 +2812,239 @@
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
         <f>'balance_raw_89563518'!$B$28</f>
         <v/>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="11">
         <f>'balance_raw_89563518'!$C$28</f>
         <v/>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="11">
         <f>'balance_raw_89563518'!$D$28</f>
         <v/>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="11">
         <f>'balance_raw_89563518'!$E$28</f>
         <v/>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="11">
         <f>'balance_raw_89563518'!$F$28</f>
         <v/>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" s="9">
+      <c r="H49" s="12">
         <f>IFERROR(B49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="12">
         <f>IFERROR(C49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="12">
         <f>IFERROR(D49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="12">
         <f>IFERROR(E49/$B$49*100,"")</f>
         <v/>
       </c>
-      <c r="L49" s="9">
+      <c r="L49" s="12">
         <f>IFERROR(F49/$B$49*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B50" s="5">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>PASSIVER t.kr.</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B52" s="5">
         <f>'balance_raw_89563518'!$B$29</f>
         <v/>
       </c>
-      <c r="C50" s="5">
+      <c r="C52" s="5">
         <f>'balance_raw_89563518'!$C$29</f>
         <v/>
       </c>
-      <c r="D50" s="5">
+      <c r="D52" s="5">
         <f>'balance_raw_89563518'!$D$29</f>
         <v/>
       </c>
-      <c r="E50" s="5">
+      <c r="E52" s="5">
         <f>'balance_raw_89563518'!$E$29</f>
         <v/>
       </c>
-      <c r="F50" s="5">
+      <c r="F52" s="5">
         <f>'balance_raw_89563518'!$F$29</f>
         <v/>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="6">
-        <f>IFERROR(B50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="6">
-        <f>IFERROR(C50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="6">
-        <f>IFERROR(D50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="6">
-        <f>IFERROR(E50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="L50" s="6">
-        <f>IFERROR(F50/$B$50*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B51" s="11">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" s="6">
+        <f>IFERROR(B52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="6">
+        <f>IFERROR(C52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="6">
+        <f>IFERROR(D52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="6">
+        <f>IFERROR(E52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="6">
+        <f>IFERROR(F52/$B$52*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
         <f>'balance_raw_89563518'!$B$30</f>
         <v/>
       </c>
-      <c r="C51" s="11">
+      <c r="C53" s="8">
         <f>'balance_raw_89563518'!$C$30</f>
         <v/>
       </c>
-      <c r="D51" s="11">
+      <c r="D53" s="8">
         <f>'balance_raw_89563518'!$D$30</f>
         <v/>
       </c>
-      <c r="E51" s="11">
+      <c r="E53" s="8">
         <f>'balance_raw_89563518'!$E$30</f>
         <v/>
       </c>
-      <c r="F51" s="11">
+      <c r="F53" s="8">
         <f>'balance_raw_89563518'!$F$30</f>
         <v/>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="12">
-        <f>IFERROR(B51/$B$51*100,"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="12">
-        <f>IFERROR(C51/$B$51*100,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="12">
-        <f>IFERROR(D51/$B$51*100,"")</f>
-        <v/>
-      </c>
-      <c r="K51" s="12">
-        <f>IFERROR(E51/$B$51*100,"")</f>
-        <v/>
-      </c>
-      <c r="L51" s="12">
-        <f>IFERROR(F51/$B$51*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B52" s="11">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" s="9">
+        <f>IFERROR(B53/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="9">
+        <f>IFERROR(C53/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="9">
+        <f>IFERROR(D53/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="9">
+        <f>IFERROR(E53/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="9">
+        <f>IFERROR(F53/$B$53*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B54" s="5">
         <f>'balance_raw_89563518'!$B$31</f>
         <v/>
       </c>
-      <c r="C52" s="11">
+      <c r="C54" s="5">
         <f>'balance_raw_89563518'!$C$31</f>
         <v/>
       </c>
-      <c r="D52" s="11">
+      <c r="D54" s="5">
         <f>'balance_raw_89563518'!$D$31</f>
         <v/>
       </c>
-      <c r="E52" s="11">
+      <c r="E54" s="5">
         <f>'balance_raw_89563518'!$E$31</f>
         <v/>
       </c>
-      <c r="F52" s="11">
+      <c r="F54" s="5">
         <f>'balance_raw_89563518'!$F$31</f>
         <v/>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" s="12">
-        <f>IFERROR(B52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="12">
-        <f>IFERROR(C52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="12">
-        <f>IFERROR(D52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="12">
-        <f>IFERROR(E52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="L52" s="12">
-        <f>IFERROR(F52/$B$52*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>PASSIVER t.kr.</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2024</v>
-      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>2024</v>
+      <c r="H54" s="6">
+        <f>IFERROR(B54/$B$54*100,"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="6">
+        <f>IFERROR(C54/$B$54*100,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="6">
+        <f>IFERROR(D54/$B$54*100,"")</f>
+        <v/>
+      </c>
+      <c r="K54" s="6">
+        <f>IFERROR(E54/$B$54*100,"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="6">
+        <f>IFERROR(F54/$B$54*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
+          <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -3091,7 +3092,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B56" s="5">
@@ -3139,7 +3140,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Reserve for udviklingsomkostninger</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -3185,49 +3186,49 @@
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B58" s="5">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B58" s="11">
         <f>'balance_raw_89563518'!$B$35</f>
         <v/>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="11">
         <f>'balance_raw_89563518'!$C$35</f>
         <v/>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="11">
         <f>'balance_raw_89563518'!$D$35</f>
         <v/>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="11">
         <f>'balance_raw_89563518'!$E$35</f>
         <v/>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="11">
         <f>'balance_raw_89563518'!$F$35</f>
         <v/>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" s="6">
+      <c r="H58" s="12">
         <f>IFERROR(B58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="I58" s="6">
+      <c r="I58" s="12">
         <f>IFERROR(C58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="J58" s="6">
+      <c r="J58" s="12">
         <f>IFERROR(D58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="12">
         <f>IFERROR(E58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="12">
         <f>IFERROR(F58/$B$58*100,"")</f>
         <v/>
       </c>
@@ -3235,7 +3236,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
       <c r="B59" s="8">
@@ -3281,97 +3282,97 @@
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B60" s="5">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B60" s="11">
         <f>'balance_raw_89563518'!$B$37</f>
         <v/>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="11">
         <f>'balance_raw_89563518'!$C$37</f>
         <v/>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="11">
         <f>'balance_raw_89563518'!$D$37</f>
         <v/>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="11">
         <f>'balance_raw_89563518'!$E$37</f>
         <v/>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="11">
         <f>'balance_raw_89563518'!$F$37</f>
         <v/>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="6">
+      <c r="H60" s="12">
         <f>IFERROR(B60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="I60" s="6">
+      <c r="I60" s="12">
         <f>IFERROR(C60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="J60" s="6">
+      <c r="J60" s="12">
         <f>IFERROR(D60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="12">
         <f>IFERROR(E60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="12">
         <f>IFERROR(F60/$B$60*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B61" s="11">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B61" s="8">
         <f>'balance_raw_89563518'!$B$38</f>
         <v/>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="8">
         <f>'balance_raw_89563518'!$C$38</f>
         <v/>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="8">
         <f>'balance_raw_89563518'!$D$38</f>
         <v/>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="8">
         <f>'balance_raw_89563518'!$E$38</f>
         <v/>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="8">
         <f>'balance_raw_89563518'!$F$38</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="12">
+      <c r="H61" s="9">
         <f>IFERROR(B61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="I61" s="12">
+      <c r="I61" s="9">
         <f>IFERROR(C61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="J61" s="12">
+      <c r="J61" s="9">
         <f>IFERROR(D61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="9">
         <f>IFERROR(E61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="L61" s="12">
+      <c r="L61" s="9">
         <f>IFERROR(F61/$B$61*100,"")</f>
         <v/>
       </c>
@@ -3379,7 +3380,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Hensættelse til udskudt skat</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3425,49 +3426,49 @@
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B63" s="11">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B63" s="8">
         <f>'balance_raw_89563518'!$B$40</f>
         <v/>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="8">
         <f>'balance_raw_89563518'!$C$40</f>
         <v/>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="8">
         <f>'balance_raw_89563518'!$D$40</f>
         <v/>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="8">
         <f>'balance_raw_89563518'!$E$40</f>
         <v/>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="8">
         <f>'balance_raw_89563518'!$F$40</f>
         <v/>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="12">
+      <c r="H63" s="9">
         <f>IFERROR(B63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="I63" s="12">
+      <c r="I63" s="9">
         <f>IFERROR(C63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="J63" s="12">
+      <c r="J63" s="9">
         <f>IFERROR(D63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="K63" s="12">
+      <c r="K63" s="9">
         <f>IFERROR(E63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="L63" s="12">
+      <c r="L63" s="9">
         <f>IFERROR(F63/$B$63*100,"")</f>
         <v/>
       </c>
@@ -3475,7 +3476,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3521,49 +3522,49 @@
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B65" s="8">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B65" s="11">
         <f>'balance_raw_89563518'!$B$42</f>
         <v/>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="11">
         <f>'balance_raw_89563518'!$C$42</f>
         <v/>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="11">
         <f>'balance_raw_89563518'!$D$42</f>
         <v/>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="11">
         <f>'balance_raw_89563518'!$E$42</f>
         <v/>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="11">
         <f>'balance_raw_89563518'!$F$42</f>
         <v/>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="9">
+      <c r="H65" s="12">
         <f>IFERROR(B65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="12">
         <f>IFERROR(C65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="J65" s="9">
+      <c r="J65" s="12">
         <f>IFERROR(D65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="K65" s="9">
+      <c r="K65" s="12">
         <f>IFERROR(E65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="L65" s="9">
+      <c r="L65" s="12">
         <f>IFERROR(F65/$B$65*100,"")</f>
         <v/>
       </c>
@@ -3571,7 +3572,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3619,7 +3620,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -3665,49 +3666,49 @@
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B68" s="11">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B68" s="5">
         <f>'balance_raw_89563518'!$B$45</f>
         <v/>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="5">
         <f>'balance_raw_89563518'!$C$45</f>
         <v/>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="5">
         <f>'balance_raw_89563518'!$D$45</f>
         <v/>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="5">
         <f>'balance_raw_89563518'!$E$45</f>
         <v/>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="5">
         <f>'balance_raw_89563518'!$F$45</f>
         <v/>
       </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" s="12">
+      <c r="H68" s="6">
         <f>IFERROR(B68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="I68" s="12">
+      <c r="I68" s="6">
         <f>IFERROR(C68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="J68" s="12">
+      <c r="J68" s="6">
         <f>IFERROR(D68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="K68" s="12">
+      <c r="K68" s="6">
         <f>IFERROR(E68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="L68" s="12">
+      <c r="L68" s="6">
         <f>IFERROR(F68/$B$68*100,"")</f>
         <v/>
       </c>
@@ -3715,7 +3716,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3763,7 +3764,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3811,7 +3812,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B71" s="8">
@@ -3859,7 +3860,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B72" s="5">
@@ -3907,7 +3908,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B73" s="8">
@@ -3955,7 +3956,7 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B74" s="5">
@@ -4003,7 +4004,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B75" s="8">
@@ -4051,7 +4052,7 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B76" s="5">
@@ -4097,727 +4098,725 @@
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B77" s="11">
         <f>'balance_raw_89563518'!$B$54</f>
         <v/>
       </c>
-      <c r="C77" s="8">
+      <c r="C77" s="11">
         <f>'balance_raw_89563518'!$C$54</f>
         <v/>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="11">
         <f>'balance_raw_89563518'!$D$54</f>
         <v/>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="11">
         <f>'balance_raw_89563518'!$E$54</f>
         <v/>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="11">
         <f>'balance_raw_89563518'!$F$54</f>
         <v/>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="9">
+      <c r="H77" s="12">
         <f>IFERROR(B77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="I77" s="9">
+      <c r="I77" s="12">
         <f>IFERROR(C77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="J77" s="9">
+      <c r="J77" s="12">
         <f>IFERROR(D77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="K77" s="9">
+      <c r="K77" s="12">
         <f>IFERROR(E77/$B$77*100,"")</f>
         <v/>
       </c>
-      <c r="L77" s="9">
+      <c r="L77" s="12">
         <f>IFERROR(F77/$B$77*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B78" s="5">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B78" s="11">
         <f>'balance_raw_89563518'!$B$55</f>
         <v/>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="11">
         <f>'balance_raw_89563518'!$C$55</f>
         <v/>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="11">
         <f>'balance_raw_89563518'!$D$55</f>
         <v/>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="11">
         <f>'balance_raw_89563518'!$E$55</f>
         <v/>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="11">
         <f>'balance_raw_89563518'!$F$55</f>
         <v/>
       </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" s="6">
+      <c r="H78" s="12">
         <f>IFERROR(B78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="I78" s="6">
+      <c r="I78" s="12">
         <f>IFERROR(C78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="J78" s="6">
+      <c r="J78" s="12">
         <f>IFERROR(D78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="12">
         <f>IFERROR(E78/$B$78*100,"")</f>
         <v/>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="12">
         <f>IFERROR(F78/$B$78*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B79" s="11">
         <f>'balance_raw_89563518'!$B$56</f>
         <v/>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="11">
         <f>'balance_raw_89563518'!$C$56</f>
         <v/>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="11">
         <f>'balance_raw_89563518'!$D$56</f>
         <v/>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="11">
         <f>'balance_raw_89563518'!$E$56</f>
         <v/>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="11">
         <f>'balance_raw_89563518'!$F$56</f>
         <v/>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" s="9">
+      <c r="H79" s="12">
         <f>IFERROR(B79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="12">
         <f>IFERROR(C79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="12">
         <f>IFERROR(D79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="K79" s="9">
+      <c r="K79" s="12">
         <f>IFERROR(E79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="L79" s="9">
+      <c r="L79" s="12">
         <f>IFERROR(F79/$B$79*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B80" s="11">
-        <f>'balance_raw_89563518'!$B$57</f>
-        <v/>
-      </c>
-      <c r="C80" s="11">
-        <f>'balance_raw_89563518'!$C$57</f>
-        <v/>
-      </c>
-      <c r="D80" s="11">
-        <f>'balance_raw_89563518'!$D$57</f>
-        <v/>
-      </c>
-      <c r="E80" s="11">
-        <f>'balance_raw_89563518'!$E$57</f>
-        <v/>
-      </c>
-      <c r="F80" s="11">
-        <f>'balance_raw_89563518'!$F$57</f>
-        <v/>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" s="12">
-        <f>IFERROR(B80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="I80" s="12">
-        <f>IFERROR(C80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="J80" s="12">
-        <f>IFERROR(D80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="K80" s="12">
-        <f>IFERROR(E80/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="L80" s="12">
-        <f>IFERROR(F80/$B$80*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B81" s="11">
-        <f>'balance_raw_89563518'!$B$58</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>'balance_raw_89563518'!$C$58</f>
-        <v/>
-      </c>
-      <c r="D81" s="11">
-        <f>'balance_raw_89563518'!$D$58</f>
-        <v/>
-      </c>
-      <c r="E81" s="11">
-        <f>'balance_raw_89563518'!$E$58</f>
-        <v/>
-      </c>
-      <c r="F81" s="11">
-        <f>'balance_raw_89563518'!$F$58</f>
-        <v/>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" s="12">
-        <f>IFERROR(B81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="I81" s="12">
-        <f>IFERROR(C81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="J81" s="12">
-        <f>IFERROR(D81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="K81" s="12">
-        <f>IFERROR(E81/$B$81*100,"")</f>
-        <v/>
-      </c>
-      <c r="L81" s="12">
-        <f>IFERROR(F81/$B$81*100,"")</f>
-        <v/>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>NØGLEOPLYSNINGER</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B82" s="11">
-        <f>'balance_raw_89563518'!$B$59</f>
-        <v/>
-      </c>
-      <c r="C82" s="11">
-        <f>'balance_raw_89563518'!$C$59</f>
-        <v/>
-      </c>
-      <c r="D82" s="11">
-        <f>'balance_raw_89563518'!$D$59</f>
-        <v/>
-      </c>
-      <c r="E82" s="11">
-        <f>'balance_raw_89563518'!$E$59</f>
-        <v/>
-      </c>
-      <c r="F82" s="11">
-        <f>'balance_raw_89563518'!$F$59</f>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B82" s="5">
+        <f>'res_raw_89563518'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C82" s="5">
+        <f>'res_raw_89563518'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D82" s="5">
+        <f>'res_raw_89563518'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E82" s="5">
+        <f>'res_raw_89563518'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F82" s="5">
+        <f>'res_raw_89563518'!$F$19</f>
         <v/>
       </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" s="12">
+      <c r="H82" s="6">
         <f>IFERROR(B82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="I82" s="12">
+      <c r="I82" s="6">
         <f>IFERROR(C82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="J82" s="12">
+      <c r="J82" s="6">
         <f>IFERROR(D82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="K82" s="12">
+      <c r="K82" s="6">
         <f>IFERROR(E82/$B$82*100,"")</f>
         <v/>
       </c>
-      <c r="L82" s="12">
+      <c r="L82" s="6">
         <f>IFERROR(F82/$B$82*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>NØGLEOPLYSNINGER</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C84" s="3" t="n">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B83" s="8">
+        <f>'res_raw_89563518'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C83" s="8">
+        <f>'res_raw_89563518'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D83" s="8">
+        <f>'res_raw_89563518'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E83" s="8">
+        <f>'res_raw_89563518'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F83" s="8">
+        <f>'res_raw_89563518'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" s="9">
+        <f>IFERROR(B83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="9">
+        <f>IFERROR(C83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="9">
+        <f>IFERROR(D83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="K83" s="9">
+        <f>IFERROR(E83/$B$83*100,"")</f>
+        <v/>
+      </c>
+      <c r="L83" s="9">
+        <f>IFERROR(F83/$B$83*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="C85" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="D85" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="E85" s="3" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B85" s="8">
-        <f>'res_raw_89563518'!$B$19</f>
-        <v/>
-      </c>
-      <c r="C85" s="8">
-        <f>'res_raw_89563518'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D85" s="8">
-        <f>'res_raw_89563518'!$D$19</f>
-        <v/>
-      </c>
-      <c r="E85" s="8">
-        <f>'res_raw_89563518'!$E$19</f>
-        <v/>
-      </c>
-      <c r="F85" s="8">
-        <f>'res_raw_89563518'!$F$19</f>
-        <v/>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" s="9">
-        <f>IFERROR(B85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="I85" s="9">
-        <f>IFERROR(C85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="J85" s="9">
-        <f>IFERROR(D85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="K85" s="9">
-        <f>IFERROR(E85/$B$85*100,"")</f>
-        <v/>
-      </c>
-      <c r="L85" s="9">
-        <f>IFERROR(F85/$B$85*100,"")</f>
-        <v/>
+      <c r="F85" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B86" s="5">
-        <f>'res_raw_89563518'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C86" s="5">
-        <f>'res_raw_89563518'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D86" s="5">
-        <f>'res_raw_89563518'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E86" s="5">
-        <f>'res_raw_89563518'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F86" s="5">
-        <f>'res_raw_89563518'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" s="6">
-        <f>IFERROR(B86/$B$86*100,"")</f>
-        <v/>
-      </c>
-      <c r="I86" s="6">
-        <f>IFERROR(C86/$B$86*100,"")</f>
-        <v/>
-      </c>
-      <c r="J86" s="6">
-        <f>IFERROR(D86/$B$86*100,"")</f>
-        <v/>
-      </c>
-      <c r="K86" s="6">
-        <f>IFERROR(E86/$B$86*100,"")</f>
-        <v/>
-      </c>
-      <c r="L86" s="6">
-        <f>IFERROR(F86/$B$86*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>2024</v>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B86" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$49*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B87" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B88" s="13">
+        <f>IFERROR($B$4/$B$49,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="13">
+        <f>IFERROR($C$4/$C$49,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="13">
+        <f>IFERROR($D$4/$D$49,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="13">
+        <f>IFERROR($E$4/$E$49,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="13">
+        <f>IFERROR($F$4/$F$49,"")</f>
+        <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B89" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$52*100,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B89" s="14">
+        <f>IFERROR($B$18/$B$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="14">
+        <f>IFERROR($C$18/$C$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="14">
+        <f>IFERROR($D$18/$D$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="14">
+        <f>IFERROR($E$18/$E$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="14">
+        <f>IFERROR($F$18/$F$58*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B90" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B90" s="13">
+        <f>IFERROR($B$16/($B$79-$B$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="13">
+        <f>IFERROR($C$16/($C$79-$C$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="13">
+        <f>IFERROR($D$16/($D$79-$D$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="13">
+        <f>IFERROR($E$16/($E$79-$E$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="13">
+        <f>IFERROR($F$16/($F$79-$F$58)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B91" s="13">
-        <f>IFERROR($B$4/$B$52,"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="13">
-        <f>IFERROR($C$4/$C$52,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="13">
-        <f>IFERROR($D$4/$D$52,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="13">
-        <f>IFERROR($E$4/$E$52,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="13">
-        <f>IFERROR($F$4/$F$52,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B91" s="14">
+        <f>IFERROR($B$58/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="14">
+        <f>IFERROR($C$58/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="14">
+        <f>IFERROR($D$58/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="14">
+        <f>IFERROR($E$58/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F91" s="14">
+        <f>IFERROR($F$58/$F$49*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B92" s="14">
-        <f>IFERROR($B$18/$B$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="14">
-        <f>IFERROR($C$18/$C$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="14">
-        <f>IFERROR($D$18/$D$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="14">
-        <f>IFERROR($E$18/$E$61*100,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="14">
-        <f>IFERROR($F$18/$F$61*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B92" s="13">
+        <f>IFERROR(($B$79-$B$58)/$B$58,"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="13">
+        <f>IFERROR(($C$79-$C$58)/$C$58,"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="13">
+        <f>IFERROR(($D$79-$D$58)/$D$58,"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="13">
+        <f>IFERROR(($E$79-$E$58)/$E$58,"")</f>
+        <v/>
+      </c>
+      <c r="F92" s="13">
+        <f>IFERROR(($F$79-$F$58)/$F$58,"")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B93" s="13">
-        <f>IFERROR($B$16/($B$82-$B$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C93" s="13">
-        <f>IFERROR($C$16/($C$82-$C$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="13">
-        <f>IFERROR($D$16/($D$82-$D$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="13">
-        <f>IFERROR($E$16/($E$82-$E$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F93" s="13">
-        <f>IFERROR($F$16/($F$82-$F$61)*100,"")</f>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B93" s="14">
+        <f>IFERROR($B$48/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="14">
+        <f>IFERROR($C$48/$C$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="D93" s="14">
+        <f>IFERROR($D$48/$D$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="14">
+        <f>IFERROR($E$48/$E$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="F93" s="14">
+        <f>IFERROR($F$48/$F$77*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B94" s="14">
-        <f>IFERROR($B$61/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="C94" s="14">
-        <f>IFERROR($C$61/$C$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="14">
-        <f>IFERROR($D$61/$D$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="14">
-        <f>IFERROR($E$61/$E$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="14">
-        <f>IFERROR($F$61/$F$52*100,"")</f>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B94" s="13">
+        <f>IFERROR(B86-B90,"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="13">
+        <f>IFERROR(C86-C90,"")</f>
+        <v/>
+      </c>
+      <c r="D94" s="13">
+        <f>IFERROR(D86-D90,"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="13">
+        <f>IFERROR(E86-E90,"")</f>
+        <v/>
+      </c>
+      <c r="F94" s="13">
+        <f>IFERROR(F86-F90,"")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B95" s="13">
-        <f>IFERROR(($B$82-$B$61)/$B$61,"")</f>
-        <v/>
-      </c>
-      <c r="C95" s="13">
-        <f>IFERROR(($C$82-$C$61)/$C$61,"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="13">
-        <f>IFERROR(($D$82-$D$61)/$D$61,"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="13">
-        <f>IFERROR(($E$82-$E$61)/$E$61,"")</f>
-        <v/>
-      </c>
-      <c r="F95" s="13">
-        <f>IFERROR(($F$82-$F$61)/$F$61,"")</f>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B95" s="14">
+        <f>IFERROR(($B$79-$B$58)/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="14">
+        <f>IFERROR(($C$79-$C$58)/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D95" s="14">
+        <f>IFERROR(($D$79-$D$58)/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="14">
+        <f>IFERROR(($E$79-$E$58)/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="14">
+        <f>IFERROR(($F$79-$F$58)/$F$49*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B96" s="14">
-        <f>IFERROR($B$51/$B$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="C96" s="14">
-        <f>IFERROR($C$51/$C$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="14">
-        <f>IFERROR($D$51/$D$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="14">
-        <f>IFERROR($E$51/$E$80*100,"")</f>
-        <v/>
-      </c>
-      <c r="F96" s="14">
-        <f>IFERROR($F$51/$F$80*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B97" s="13">
-        <f>IFERROR(B89-B93,"")</f>
-        <v/>
-      </c>
-      <c r="C97" s="13">
-        <f>IFERROR(C89-C93,"")</f>
-        <v/>
-      </c>
-      <c r="D97" s="13">
-        <f>IFERROR(D89-D93,"")</f>
-        <v/>
-      </c>
-      <c r="E97" s="13">
-        <f>IFERROR(E89-E93,"")</f>
-        <v/>
-      </c>
-      <c r="F97" s="13">
-        <f>IFERROR(F89-F93,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B98" s="14">
-        <f>IFERROR(($B$82-$B$61)/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="C98" s="14">
-        <f>IFERROR(($C$82-$C$61)/$C$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="D98" s="14">
-        <f>IFERROR(($D$82-$D$61)/$D$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="14">
-        <f>IFERROR(($E$82-$E$61)/$E$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="F98" s="14">
-        <f>IFERROR(($F$82-$F$61)/$F$52*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B99" s="13">
-        <f>IFERROR($B$36/($B$61+$B$68)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C99" s="13">
-        <f>IFERROR($C$36/($C$61+$C$68)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D99" s="13">
-        <f>IFERROR($D$36/($D$61+$D$68)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E99" s="13">
-        <f>IFERROR($E$36/($E$61+$E$68)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="13">
-        <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+      <c r="B96" s="13">
+        <f>IFERROR($B$33/($B$58+$B$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="13">
+        <f>IFERROR($C$33/($C$58+$C$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D96" s="13">
+        <f>IFERROR($D$33/($D$58+$D$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="13">
+        <f>IFERROR($E$33/($E$58+$E$65)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="13">
+        <f>IFERROR($F$33/($F$58+$F$65)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_89563518'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_89563518'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_89563518'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_89563518'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_89563518'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_89563518'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_89563518'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_89563518'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_89563518'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_89563518'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_89563518'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_89563518'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_89563518'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_89563518'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_89563518'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_89563518'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_89563518'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_89563518'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_89563518'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_89563518'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B103">
+        <f>IF(ABS(('pengestrom_raw_89563518'!$B$2+'pengestrom_raw_89563518'!$B$3+'pengestrom_raw_89563518'!$B$4)-'pengestrom_raw_89563518'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_89563518'!$B$2+'pengestrom_raw_89563518'!$B$3+'pengestrom_raw_89563518'!$B$4)-'pengestrom_raw_89563518'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C103">
+        <f>IF(ABS(('pengestrom_raw_89563518'!$C$2+'pengestrom_raw_89563518'!$C$3+'pengestrom_raw_89563518'!$C$4)-'pengestrom_raw_89563518'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_89563518'!$C$2+'pengestrom_raw_89563518'!$C$3+'pengestrom_raw_89563518'!$C$4)-'pengestrom_raw_89563518'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D103">
+        <f>IF(ABS(('pengestrom_raw_89563518'!$D$2+'pengestrom_raw_89563518'!$D$3+'pengestrom_raw_89563518'!$D$4)-'pengestrom_raw_89563518'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_89563518'!$D$2+'pengestrom_raw_89563518'!$D$3+'pengestrom_raw_89563518'!$D$4)-'pengestrom_raw_89563518'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E103">
+        <f>IF(ABS(('pengestrom_raw_89563518'!$E$2+'pengestrom_raw_89563518'!$E$3+'pengestrom_raw_89563518'!$E$4)-'pengestrom_raw_89563518'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_89563518'!$E$2+'pengestrom_raw_89563518'!$E$3+'pengestrom_raw_89563518'!$E$4)-'pengestrom_raw_89563518'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F103">
+        <f>IF(ABS(('pengestrom_raw_89563518'!$F$2+'pengestrom_raw_89563518'!$F$3+'pengestrom_raw_89563518'!$F$4)-'pengestrom_raw_89563518'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_89563518'!$F$2+'pengestrom_raw_89563518'!$F$3+'pengestrom_raw_89563518'!$F$4)-'pengestrom_raw_89563518'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4850,410 +4849,408 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>396297</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>567121</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>662284</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>707353</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>739008</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>854000</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>907</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>19628</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>10098</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>7222</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>7898</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>8818</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>197717</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>67554</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>70570</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>67696</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>68017</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>695004</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>60540</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>425780</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>522994</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>542630</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>561215</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>71380</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>138947</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>141341</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>139290</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>164723</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>177793</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>159000</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>96497</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>102139</v>
       </c>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n">
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n">
         <v>169264</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>176809</v>
       </c>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>19319</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>19624</v>
       </c>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>8295</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>2228</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>1619</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>1451</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>8637</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>23131</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>37219</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>25791</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>48112</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>57068</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>29000</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>2376</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>616</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>6352</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>2794</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Finansielle omkostninger</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>6126</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>7608</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>12533</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>12880</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>10132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Finansielle poster, netto</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="D15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1014</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>616</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>6352</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>2794</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Finansielle omkostninger</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>1961</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>6126</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>7608</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>12533</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>12880</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle poster, netto</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n">
-        <v>-7000</v>
-      </c>
-      <c r="E15" s="16" t="n">
+      <c r="F15" s="17" t="n">
+        <v>-8000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Resultat før skat</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>32107</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>18799</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>41931</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>46982</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>20804</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Skat af årets resultat</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>8504</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>4235</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>9959</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>11495</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>8294</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Årets resultat</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>23603</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>14564</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>31972</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>35487</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>477</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>488</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>471</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>435</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D20" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Resultat før skat</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>23546</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>32107</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>18799</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>41931</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>46982</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Skat af årets resultat</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>4922</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>8504</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>4235</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>9959</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>11495</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Årets resultat</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>18624</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>23603</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>14564</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>31972</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>35487</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>179</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>477</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>488</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>471</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>29000</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>19000</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>0</v>
+      <c r="F20" s="17" t="n">
+        <v>39000</v>
       </c>
     </row>
   </sheetData>
@@ -5267,7 +5264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5285,1151 +5282,1097 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>20322</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>17505</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>14741</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>12293</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>2750</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>1100</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>900</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>500</v>
       </c>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>7232</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>21959</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>19129</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>16333</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>13516</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>10698</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>22112</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>43411</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>38045</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>32894</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>29846</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>22930</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>185040</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>177068</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>175249</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>170961</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>167206</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>50300</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>76624</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>86373</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>85024</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>84475</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>159248</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>1757</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>6512</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>6058</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>5574</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>4960</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>5873</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>14437</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>22942</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>14184</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>52495</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>85670</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>23460</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>152652</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>291118</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>283683</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>318342</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>346066</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>355787</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>59349</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0</v>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>334529</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>321728</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>351236</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>375912</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>379000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Deposita</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>54128</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>62536</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>61886</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>68427</v>
+      </c>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>59349</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0</v>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n">
+        <v>72536</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>234113</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>334529</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>321728</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>351236</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>375912</v>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>33672</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>30015</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>42121</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>44882</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>49542</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Råvarer og hjælpematerialer</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n">
-        <v>54128</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>62536</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>61886</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>68427</v>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>87800</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>92551</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>104007</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>113309</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>122078</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Varer under fremstilling</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>67822</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>114792</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>100532</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>117417</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>117294</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Færdigvarer og handelsvarer</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n">
-        <v>33672</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>30015</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>42121</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>44882</v>
-      </c>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>264</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>371</v>
+      </c>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>49782</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>87800</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>92551</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>104007</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>113309</v>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>17212</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>6479</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>5103</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>5068</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>7050</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>59630</v>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>67822</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>114792</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>100532</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>117417</v>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>2156</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>989</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>3687</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>1797</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>990</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>202</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>264</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>371</v>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>5912</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>5225</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>4063</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>4579</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>3333</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>17212</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>6479</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>5103</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>5068</v>
-      </c>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>461</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>2156</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>989</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>3209</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>3687</v>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>1705</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>1170</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>261</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n">
-        <v>5912</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>5225</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>4063</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>4579</v>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>128726</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>114551</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>131383</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>131269</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>866</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>1705</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>1170</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>1380</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>261</v>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>12595</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>8022</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>6239</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>6239</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>17056</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>63137</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>95009</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>128726</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>114551</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>131383</v>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>195404</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>229299</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>224797</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>267218</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>270000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>529933</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>551027</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>576033</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>643130</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>649000</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>372</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>12595</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>8022</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>6239</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>6239</v>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>113291</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>195404</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>229299</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>224797</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>267218</v>
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>347405</v>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>529933</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>551027</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>576033</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>643130</v>
-      </c>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>4000</v>
-      </c>
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n">
-        <v>29245</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>-415</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>328</v>
+      </c>
+      <c r="D33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>0</v>
+      <c r="E33" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>3992</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>184747</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>199325</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>231283</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>246762</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>249272</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>189557</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>203290</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>239273</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>241180</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>269000</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n">
-        <v>-415</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>328</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>102</v>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>10447</v>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>11349</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>10976</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>12169</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>11800</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>130682</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>184747</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>199325</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>231283</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>246762</v>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>11355</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>11594</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>11261</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>12634</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>12258</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>163926</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>189557</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>203290</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>239273</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>241180</v>
-      </c>
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>7783</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>10447</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>11349</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>10976</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>12169</v>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>20082</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>16246</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>12357</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>8209</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>3944</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>7783</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>11355</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>11594</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>11261</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>12634</v>
-      </c>
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>8832</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>24175</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>20082</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>16246</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>12357</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>8209</v>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>28914</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>25247</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>21369</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>17085</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>12950</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>8999</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>8832</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>9001</v>
-      </c>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>4093</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>3865</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>3929</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>4141</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>4255</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>33174</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>28914</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>25247</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>21369</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>17085</v>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>194685</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>191602</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>200580</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>212895</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>227693</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>4093</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>4093</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>3865</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>3929</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>4141</v>
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>48948</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>59646</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>55481</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>73425</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>77922</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>62228</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>194685</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>191602</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>200580</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>212895</v>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>15233</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>224</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>30908</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>48948</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>59646</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>55481</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>73425</v>
-      </c>
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>4055</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>5287</v>
+      </c>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>2627</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>15233</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>224</v>
-      </c>
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>50369</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>39045</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>39647</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>40944</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>42807</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n">
-        <v>156</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>4055</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>5287</v>
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>438</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>963</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>879</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>300107</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>310896</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>304130</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>337879</v>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>354527</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="n">
-        <v>41272</v>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>50369</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>39045</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>39647</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>40944</v>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>329021</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>336143</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>325499</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>354964</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>367477</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>1394</v>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>1856</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>438</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="n">
-        <v>142522</v>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>300107</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>310896</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>304130</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>337879</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>175696</v>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>329021</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>336143</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>325499</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>354964</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
-        <v>347405</v>
-      </c>
-      <c r="C59" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>529933</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>551027</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>576033</v>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>643130</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>649120</v>
       </c>
     </row>
   </sheetData>
@@ -6438,6 +6381,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>37726</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>9018</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>63950</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>66394</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-91334</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-21613</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-55896</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-58350</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>55332</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>8022</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-9837</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>8243</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-9000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6468,13 +6533,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6806,15 +6871,15 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>'balance_raw_89563518'!$F$15</f>
+        <f>'balance_raw_89563518'!$F$12</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>'balance_raw_89563518'!$E$15</f>
+        <f>'balance_raw_89563518'!$E$12</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>'balance_raw_89563518'!$D$15</f>
+        <f>'balance_raw_89563518'!$D$12</f>
         <v/>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -6830,15 +6895,15 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>'balance_raw_89563518'!$F$30</f>
+        <f>'balance_raw_89563518'!$F$27</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>'balance_raw_89563518'!$E$30</f>
+        <f>'balance_raw_89563518'!$E$27</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>'balance_raw_89563518'!$D$30</f>
+        <f>'balance_raw_89563518'!$D$27</f>
         <v/>
       </c>
       <c r="F20" s="25" t="inlineStr">
@@ -6885,15 +6950,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw_89563518'!$F$38</f>
+        <f>'balance_raw_89563518'!$F$35</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw_89563518'!$E$38</f>
+        <f>'balance_raw_89563518'!$E$35</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw_89563518'!$D$38</f>
+        <f>'balance_raw_89563518'!$D$35</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -6909,15 +6974,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_89563518'!$F$59-'balance_raw_89563518'!$F$38</f>
+        <f>'balance_raw_89563518'!$F$56-'balance_raw_89563518'!$F$35</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_89563518'!$E$59-'balance_raw_89563518'!$E$38</f>
+        <f>'balance_raw_89563518'!$E$56-'balance_raw_89563518'!$E$35</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_89563518'!$D$59-'balance_raw_89563518'!$D$38</f>
+        <f>'balance_raw_89563518'!$D$56-'balance_raw_89563518'!$D$35</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6975,15 +7040,15 @@
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw_89563518'!$F$19</f>
+        <f>'balance_raw_89563518'!$F$16</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw_89563518'!$E$19</f>
+        <f>'balance_raw_89563518'!$E$16</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw_89563518'!$D$19</f>
+        <f>'balance_raw_89563518'!$D$16</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -6999,15 +7064,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw_89563518'!$F$20</f>
+        <f>'balance_raw_89563518'!$F$17</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw_89563518'!$E$20</f>
+        <f>'balance_raw_89563518'!$E$17</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw_89563518'!$D$20</f>
+        <f>'balance_raw_89563518'!$D$17</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -7023,15 +7088,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_89563518'!$F$57</f>
+        <f>'balance_raw_89563518'!$F$54</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_89563518'!$E$57</f>
+        <f>'balance_raw_89563518'!$E$54</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_89563518'!$D$57</f>
+        <f>'balance_raw_89563518'!$D$54</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -7188,7 +7253,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7306,7 +7371,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7482,7 +7547,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7515,15 +7580,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_89563518'!$F$31="","—",IF(ABS(B21-'balance_raw_89563518'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_89563518'!$F$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_89563518'!$F$28="","—",IF(ABS(B21-'balance_raw_89563518'!$F$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_89563518'!$F$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_89563518'!$E$31="","—",IF(ABS(C21-'balance_raw_89563518'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_89563518'!$E$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_89563518'!$E$28="","—",IF(ABS(C21-'balance_raw_89563518'!$E$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_89563518'!$E$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_89563518'!$D$31="","—",IF(ABS(D21-'balance_raw_89563518'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_89563518'!$D$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_89563518'!$D$28="","—",IF(ABS(D21-'balance_raw_89563518'!$D$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_89563518'!$D$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -7539,15 +7604,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_89563518'!$F$59="","—",IF(ABS(B25-'balance_raw_89563518'!$F$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_89563518'!$F$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_89563518'!$F$56="","—",IF(ABS(B25-'balance_raw_89563518'!$F$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_89563518'!$F$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_89563518'!$E$59="","—",IF(ABS(C25-'balance_raw_89563518'!$E$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_89563518'!$E$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_89563518'!$E$56="","—",IF(ABS(C25-'balance_raw_89563518'!$E$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_89563518'!$E$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_89563518'!$D$59="","—",IF(ABS(D25-'balance_raw_89563518'!$D$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_89563518'!$D$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_89563518'!$D$56="","—",IF(ABS(D25-'balance_raw_89563518'!$D$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_89563518'!$D$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7660,13 +7725,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7705,27 +7770,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7752,10 +7817,10 @@
       </c>
       <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n">
+      <c r="F3" s="35" t="n">
         <v>2</v>
       </c>
+      <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7779,9 +7844,7 @@
           <t>fsa:Dividend</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n"/>
       <c r="G4" s="38" t="n"/>
@@ -7800,26 +7863,20 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+          <t>fsa:ExtraordinaryPaymentsOutflow</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+          <t>fsa:ExtraordinaryPaymentsOutflow</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n">
-        <v>46</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" s="35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
       <c r="H5" s="35" t="n">
-        <v>20</v>
+        <v>8380</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7835,28 +7892,208 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="38" t="n"/>
+      <c r="I6" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
           <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n">
+      <c r="D7" s="35" t="n">
         <v>-674</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="E7" s="35" t="n">
         <v>-2248</v>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="F7" s="35" t="n">
         <v>2091</v>
       </c>
-      <c r="H6" s="38" t="n">
+      <c r="G7" s="35" t="n">
         <v>2761</v>
       </c>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermInvestmentsInGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n"/>
+      <c r="H8" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermReceivablesDividendsFromGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermReceivablesDividendsFromGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n">
+        <v>1755</v>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>fsa:TrademarksOriginatingFromDevelopmentProjects</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>fsa:TrademarksOriginatingFromDevelopmentProjects</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n">
+        <v>300</v>
+      </c>
+      <c r="I10" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:TransferredFromSharePremium</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:TransferredFromSharePremium</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n">
+        <v>12510</v>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>fsa:VatAndDutiesPayables</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>fsa:VatAndDutiesPayables</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n"/>
+      <c r="H12" s="38" t="n">
+        <v>931</v>
+      </c>
+      <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
